--- a/TablasAnalisis/Establecimientos_de_salud_por_provincia.xlsx
+++ b/TablasAnalisis/Establecimientos_de_salud_por_provincia.xlsx
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>cantidad_establecimientos_privados_con_intensiva</t>
+          <t>cantidad_establecimientos_privados</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>cantidad_establecimientos_estatales_con_intensiva</t>
+          <t>cantidad_establecimientos_estatales</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>199</v>
+        <v>5977</v>
       </c>
       <c r="C2" t="n">
-        <v>129</v>
+        <v>3764</v>
       </c>
       <c r="D2" t="n">
         <v>9773</v>
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>1524</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="D3" t="n">
         <v>1761</v>
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>172</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>392</v>
       </c>
       <c r="D4" t="n">
         <v>566</v>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>489</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>477</v>
       </c>
       <c r="D5" t="n">
         <v>975</v>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>747</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="D6" t="n">
         <v>955</v>
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>419</v>
       </c>
       <c r="D7" t="n">
         <v>713</v>
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>2551</v>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>961</v>
       </c>
       <c r="D8" t="n">
         <v>3515</v>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>699</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>452</v>
       </c>
       <c r="D9" t="n">
         <v>1158</v>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
         <v>473</v>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>283</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>389</v>
       </c>
       <c r="D11" t="n">
         <v>673</v>
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>559</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>703</v>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>288</v>
       </c>
       <c r="D13" t="n">
         <v>449</v>
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>1741</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>505</v>
       </c>
       <c r="D14" t="n">
         <v>2263</v>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>561</v>
       </c>
       <c r="D15" t="n">
         <v>953</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>1007</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D16" t="n">
         <v>1288</v>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>367</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>233</v>
       </c>
       <c r="D17" t="n">
         <v>605</v>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>521</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>593</v>
       </c>
       <c r="D18" t="n">
         <v>1121</v>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>686</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>192</v>
       </c>
       <c r="D19" t="n">
         <v>880</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>370</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="D20" t="n">
         <v>574</v>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>351</v>
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>1688</v>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>849</v>
       </c>
       <c r="D22" t="n">
         <v>2548</v>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>653</v>
       </c>
       <c r="D23" t="n">
         <v>866</v>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>381</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D24" t="n">
         <v>446</v>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>1946</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>429</v>
       </c>
       <c r="D25" t="n">
         <v>2402</v>
